--- a/companies/dev-mini/Finance/FY2020 Financial Summary.xlsx
+++ b/companies/dev-mini/Finance/FY2020 Financial Summary.xlsx
@@ -474,20 +474,20 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>220867</v>
+        <v>211315</v>
       </c>
       <c r="C4" s="3">
-        <v>271886</v>
+        <v>260127</v>
       </c>
       <c r="D4" s="3">
-        <v>201823</v>
+        <v>193095</v>
       </c>
       <c r="E4" s="3">
-        <v>253424</v>
+        <v>242463</v>
       </c>
       <c r="F4" s="4">
         <f>SUM(B4:E4)</f>
-        <v>948000</v>
+        <v>907000</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -507,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="3">
-        <v>413900</v>
+        <v>424500</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -515,7 +515,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="3">
-        <v>92800</v>
+        <v>95200</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3">
-        <v>70470</v>
+        <v>69150</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -531,7 +531,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="3">
-        <v>56450</v>
+        <v>57900</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -539,7 +539,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="3">
-        <v>59890</v>
+        <v>61420</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -548,7 +548,7 @@
       </c>
       <c r="F12" s="4">
         <f>SUM(F7:F11)</f>
-        <v>693510</v>
+        <v>708170</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -557,7 +557,7 @@
       </c>
       <c r="F14" s="4">
         <f>F4-F12</f>
-        <v>254490</v>
+        <v>198830</v>
       </c>
     </row>
   </sheetData>
